--- a/Fixing the bug/Output_comparison.xlsx
+++ b/Fixing the bug/Output_comparison.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Actual sales" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>MONTH</t>
   </si>
@@ -37,6 +38,12 @@
   </si>
   <si>
     <t xml:space="preserve">Feature engineering done. Details of feature engineering done is captured in the .txt file. </t>
+  </si>
+  <si>
+    <t>NAME_MONTH_OF_SALE</t>
+  </si>
+  <si>
+    <t>NET_SALES</t>
   </si>
 </sst>
 </file>
@@ -45,7 +52,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -113,14 +120,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -131,6 +135,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -417,105 +425,105 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.1796875" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>46174</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>279580.96000000002</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="6">
+      <c r="A3" s="8"/>
+      <c r="B3" s="5">
         <v>46204</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>55206.11</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="6">
+      <c r="A4" s="8"/>
+      <c r="B4" s="5">
         <v>46235</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>53696.27</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>46174</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>393843.48</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="5">
         <v>46204</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>343243.15</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="5">
         <v>46235</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>349956.57</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46174</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>297713.28999999998</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="5">
         <v>46204</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>269898.75</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="5">
         <v>46235</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>276193.67</v>
       </c>
     </row>
@@ -528,4 +536,121 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>44713</v>
+      </c>
+      <c r="B2">
+        <v>396867</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>44743</v>
+      </c>
+      <c r="B3">
+        <v>311621</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>44774</v>
+      </c>
+      <c r="B4">
+        <v>316920</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>45078</v>
+      </c>
+      <c r="B5">
+        <v>470484</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>45108</v>
+      </c>
+      <c r="B6">
+        <v>396253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>45139</v>
+      </c>
+      <c r="B7">
+        <v>434805</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>45444</v>
+      </c>
+      <c r="B8">
+        <v>510565</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>45474</v>
+      </c>
+      <c r="B9">
+        <v>466085</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>45505</v>
+      </c>
+      <c r="B10">
+        <v>410425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>45809</v>
+      </c>
+      <c r="B11">
+        <v>401428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>45839</v>
+      </c>
+      <c r="B12">
+        <v>328748</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>45870</v>
+      </c>
+      <c r="B13">
+        <v>331076</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Fixing the bug/Output_comparison.xlsx
+++ b/Fixing the bug/Output_comparison.xlsx
@@ -543,7 +543,8 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">

--- a/Fixing the bug/Output_comparison.xlsx
+++ b/Fixing the bug/Output_comparison.xlsx
@@ -4,12 +4,15 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Actual sales" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Actual sales'!$A$1:$B$13</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -20,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>MONTH</t>
   </si>
@@ -37,13 +40,16 @@
     <t>No feature engineering. Swapped Covariates with previous year i.e., 2025 covariates</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature engineering done. Details of feature engineering done is captured in the .txt file. </t>
-  </si>
-  <si>
     <t>NAME_MONTH_OF_SALE</t>
   </si>
   <si>
     <t>NET_SALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature engineering done. </t>
+  </si>
+  <si>
+    <t>Best val_loss</t>
   </si>
 </sst>
 </file>
@@ -120,7 +126,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -139,6 +145,9 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -421,15 +430,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.1796875" customWidth="1"/>
     <col min="2" max="2" width="7.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -439,8 +449,11 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -450,8 +463,11 @@
       <c r="C2" s="2">
         <v>279580.96000000002</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D2" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8"/>
       <c r="B3" s="5">
         <v>46204</v>
@@ -459,8 +475,9 @@
       <c r="C3" s="2">
         <v>55206.11</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="5">
         <v>46235</v>
@@ -468,8 +485,9 @@
       <c r="C4" s="2">
         <v>53696.27</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:4" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -479,8 +497,11 @@
       <c r="C5" s="3">
         <v>393843.48</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D5" s="9">
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8"/>
       <c r="B6" s="5">
         <v>46204</v>
@@ -488,8 +509,9 @@
       <c r="C6" s="3">
         <v>343243.15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8"/>
       <c r="B7" s="5">
         <v>46235</v>
@@ -497,10 +519,11 @@
       <c r="C7" s="3">
         <v>349956.57</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5">
         <v>46174</v>
@@ -508,8 +531,11 @@
       <c r="C8" s="3">
         <v>297713.28999999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D8" s="9">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8"/>
       <c r="B9" s="5">
         <v>46204</v>
@@ -517,8 +543,9 @@
       <c r="C9" s="3">
         <v>269898.75</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
       <c r="B10" s="5">
         <v>46235</v>
@@ -526,12 +553,16 @@
       <c r="C10" s="3">
         <v>276193.67</v>
       </c>
+      <c r="D10" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D5:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -540,6 +571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -549,10 +581,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -563,7 +595,7 @@
         <v>396867</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>44743</v>
       </c>
@@ -571,7 +603,7 @@
         <v>311621</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>44774</v>
       </c>
@@ -587,7 +619,7 @@
         <v>470484</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>45108</v>
       </c>
@@ -595,7 +627,7 @@
         <v>396253</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>45139</v>
       </c>
@@ -611,7 +643,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>45474</v>
       </c>
@@ -619,7 +651,7 @@
         <v>466085</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>45505</v>
       </c>
@@ -635,7 +667,7 @@
         <v>401428</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>45839</v>
       </c>
@@ -643,7 +675,7 @@
         <v>328748</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>45870</v>
       </c>
@@ -652,6 +684,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B13">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2025" month="6" dateTimeGrouping="month"/>
+        <dateGroupItem year="2024" month="6" dateTimeGrouping="month"/>
+        <dateGroupItem year="2023" month="6" dateTimeGrouping="month"/>
+        <dateGroupItem year="2022" month="6" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Fixing the bug/Output_comparison.xlsx
+++ b/Fixing the bug/Output_comparison.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F5B3F309E2E8DDEEA5CD228132EA688CA8CCA25E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A330753-601A-4159-8270-2BFE3C47A021}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Actual sales" sheetId="2" r:id="rId2"/>
+    <sheet name="Previous year June sales" sheetId="5" r:id="rId2"/>
+    <sheet name="Previous year August sales" sheetId="4" r:id="rId3"/>
+    <sheet name="Previous years July sales" sheetId="3" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Actual sales'!$A$1:$B$13</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>MONTH</t>
   </si>
@@ -50,12 +50,30 @@
   </si>
   <si>
     <t>Best val_loss</t>
+  </si>
+  <si>
+    <t>Training Window</t>
+  </si>
+  <si>
+    <t>Validation Window</t>
+  </si>
+  <si>
+    <t>Test Window</t>
+  </si>
+  <si>
+    <t>Apr'23 to Feb'26</t>
+  </si>
+  <si>
+    <t>Mar'26 to May'26</t>
+  </si>
+  <si>
+    <t>Jun'26 to Aug'26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -98,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -121,12 +139,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -148,6 +188,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -429,17 +475,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.36328125" customWidth="1"/>
     <col min="2" max="2" width="7.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -452,8 +501,17 @@
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -466,8 +524,17 @@
       <c r="D2" s="9">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8"/>
       <c r="B3" s="5">
         <v>46204</v>
@@ -476,8 +543,11 @@
         <v>55206.11</v>
       </c>
       <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="5">
         <v>46235</v>
@@ -486,8 +556,11 @@
         <v>53696.27</v>
       </c>
       <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:4" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -500,8 +573,17 @@
       <c r="D5" s="9">
         <v>4.2000000000000003E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8"/>
       <c r="B6" s="5">
         <v>46204</v>
@@ -510,8 +592,11 @@
         <v>343243.15</v>
       </c>
       <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8"/>
       <c r="B7" s="5">
         <v>46235</v>
@@ -520,8 +605,11 @@
         <v>349956.57</v>
       </c>
       <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:4" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="1:7" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>7</v>
       </c>
@@ -534,8 +622,17 @@
       <c r="D8" s="9">
         <v>3.5999999999999997E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8"/>
       <c r="B9" s="5">
         <v>46204</v>
@@ -544,8 +641,11 @@
         <v>269898.75</v>
       </c>
       <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
       <c r="B10" s="5">
         <v>46235</v>
@@ -554,9 +654,21 @@
         <v>276193.67</v>
       </c>
       <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="15">
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:F10"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -570,13 +682,62 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:B13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B7E857-1B42-4A34-B993-B3D8192CBC86}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>44713</v>
+      </c>
+      <c r="B2">
+        <v>396867</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>45078</v>
+      </c>
+      <c r="B3">
+        <v>470484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>45444</v>
+      </c>
+      <c r="B4">
+        <v>510565</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>45809</v>
+      </c>
+      <c r="B5">
+        <v>401428</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4D78E8-41DC-40FA-AAE4-6A0E5D0F0A54}">
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.6328125" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="1" max="1" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -589,111 +750,91 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="B2">
-        <v>396867</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+        <v>316920</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
-        <v>44743</v>
+        <v>45139</v>
       </c>
       <c r="B3">
-        <v>311621</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+        <v>434805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
-        <v>44774</v>
+        <v>45505</v>
       </c>
       <c r="B4">
-        <v>316920</v>
+        <v>410425</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
-        <v>45078</v>
+        <v>45870</v>
       </c>
       <c r="B5">
-        <v>470484</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+        <v>331076</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0623659C-6E22-46CC-90A7-B75BE5ED776F}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>44743</v>
+      </c>
+      <c r="B2">
+        <v>311621</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
         <v>45108</v>
       </c>
-      <c r="B6">
+      <c r="B3">
         <v>396253</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
-        <v>45139</v>
-      </c>
-      <c r="B7">
-        <v>434805</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
-        <v>45444</v>
-      </c>
-      <c r="B8">
-        <v>510565</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
         <v>45474</v>
       </c>
-      <c r="B9">
+      <c r="B4">
         <v>466085</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
-        <v>45505</v>
-      </c>
-      <c r="B10">
-        <v>410425</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
-        <v>45809</v>
-      </c>
-      <c r="B11">
-        <v>401428</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
         <v>45839</v>
       </c>
-      <c r="B12">
+      <c r="B5">
         <v>328748</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
-        <v>45870</v>
-      </c>
-      <c r="B13">
-        <v>331076</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B13">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="6" dateTimeGrouping="month"/>
-        <dateGroupItem year="2024" month="6" dateTimeGrouping="month"/>
-        <dateGroupItem year="2023" month="6" dateTimeGrouping="month"/>
-        <dateGroupItem year="2022" month="6" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>